--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.53004656819757</v>
+        <v>3.336132567332106</v>
       </c>
       <c r="D2" t="n">
-        <v>15.8249671127931</v>
+        <v>2.571557155828879</v>
       </c>
       <c r="E2" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F2" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.47477269138061</v>
+        <v>4.139650562349349</v>
       </c>
       <c r="D3" t="n">
-        <v>8.221473566170722</v>
+        <v>1.335989454502742</v>
       </c>
       <c r="E3" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F3" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.0385087250262</v>
+        <v>6.181257667816759</v>
       </c>
       <c r="D4" t="n">
-        <v>22.64570781560156</v>
+        <v>3.679927520035253</v>
       </c>
       <c r="E4" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F4" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.71919519426754</v>
+        <v>6.454369219068476</v>
       </c>
       <c r="D5" t="n">
-        <v>7.486131332010623</v>
+        <v>1.216496341451726</v>
       </c>
       <c r="E5" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F5" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.22717604259039</v>
+        <v>3.936916106920938</v>
       </c>
       <c r="D6" t="n">
-        <v>24.34532025142238</v>
+        <v>3.956114540856137</v>
       </c>
       <c r="E6" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F6" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.38404936553324</v>
+        <v>6.237408021899152</v>
       </c>
       <c r="D7" t="n">
-        <v>27.56882297088507</v>
+        <v>4.479933732768823</v>
       </c>
       <c r="E7" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F7" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.04540038572871</v>
+        <v>2.769877562680915</v>
       </c>
       <c r="D8" t="n">
-        <v>17.30851189569738</v>
+        <v>2.812633183050824</v>
       </c>
       <c r="E8" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F8" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.33649450282962</v>
+        <v>6.392180356709813</v>
       </c>
       <c r="D9" t="n">
-        <v>39.34283032223629</v>
+        <v>6.393209927363397</v>
       </c>
       <c r="E9" t="n">
-        <v>8.852248602372294</v>
+        <v>1.438490397885498</v>
       </c>
       <c r="F9" t="n">
-        <v>9.851258262332639</v>
+        <v>1.600829467629054</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
